--- a/Module 8 Data/PowerBI Training/Labs & Quizes/labs_and_quizzes.xlsx
+++ b/Module 8 Data/PowerBI Training/Labs & Quizes/labs_and_quizzes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FrancisClass-Peters\Desktop\WSA\reStart\Analysis\Generate Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amalitech-my.sharepoint.com/personal/ernest_kwisanga_amalitech_com/Documents/Desktop/Moodle Labs/Specilization/DEM08/Module 8 Data/PowerBI Training/Labs &amp; Quizes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD2B591-90D9-42D6-9C45-74BCDADC0DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{FFD2B591-90D9-42D6-9C45-74BCDADC0DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE0ECB31-4BF9-4005-AD50-927663C58016}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Labs" sheetId="1" r:id="rId1"/>
@@ -722,12 +722,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -797,7 +797,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -832,7 +832,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -867,7 +867,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -902,7 +902,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -937,7 +937,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -972,7 +972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>47</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>54</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>64</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>75</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>90</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>91</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>93</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>95</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>96</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>98</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>100</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>101</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>102</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>103</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>105</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>106</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>108</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>109</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>110</v>
       </c>
@@ -4270,9 +4270,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4307,7 +4310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4342,7 +4345,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4377,7 +4380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -4412,7 +4415,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -4447,7 +4450,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4482,7 +4485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4517,7 +4520,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -4552,7 +4555,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4587,7 +4590,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -4622,7 +4625,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -4657,7 +4660,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -4692,7 +4695,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -4727,7 +4730,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -4762,7 +4765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -4797,7 +4800,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -4832,7 +4835,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -4867,7 +4870,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -4902,7 +4905,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -4937,7 +4940,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -4972,7 +4975,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -5007,7 +5010,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -5042,7 +5045,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -5077,7 +5080,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -5112,7 +5115,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -5147,7 +5150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -5182,7 +5185,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -5217,7 +5220,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -5252,7 +5255,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -5287,7 +5290,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -5322,7 +5325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -5357,7 +5360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -5392,7 +5395,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -5427,7 +5430,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -5462,7 +5465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -5497,7 +5500,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -5532,7 +5535,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -5567,7 +5570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>47</v>
       </c>
@@ -5602,7 +5605,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -5637,7 +5640,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -5672,7 +5675,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -5707,7 +5710,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -5742,7 +5745,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -5777,7 +5780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -5812,7 +5815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>54</v>
       </c>
@@ -5847,7 +5850,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -5882,7 +5885,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -5917,7 +5920,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -5952,7 +5955,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -5987,7 +5990,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -6022,7 +6025,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -6057,7 +6060,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -6092,7 +6095,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -6127,7 +6130,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -6162,7 +6165,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>64</v>
       </c>
@@ -6197,7 +6200,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -6232,7 +6235,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -6267,7 +6270,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -6302,7 +6305,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -6337,7 +6340,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -6372,7 +6375,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -6407,7 +6410,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -6442,7 +6445,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -6477,7 +6480,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -6512,7 +6515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -6547,7 +6550,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>75</v>
       </c>
@@ -6582,7 +6585,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -6617,7 +6620,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -6652,7 +6655,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -6687,7 +6690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -6722,7 +6725,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -6757,7 +6760,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -6792,7 +6795,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -6827,7 +6830,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -6862,7 +6865,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -6897,7 +6900,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -6932,7 +6935,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -6967,7 +6970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -7002,7 +7005,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -7037,7 +7040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -7072,7 +7075,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>90</v>
       </c>
@@ -7107,7 +7110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>91</v>
       </c>
@@ -7142,7 +7145,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -7177,7 +7180,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>93</v>
       </c>
@@ -7212,7 +7215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -7247,7 +7250,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>95</v>
       </c>
@@ -7282,7 +7285,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>96</v>
       </c>
@@ -7317,7 +7320,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -7352,7 +7355,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>98</v>
       </c>
@@ -7387,7 +7390,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -7422,7 +7425,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>100</v>
       </c>
@@ -7457,7 +7460,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>101</v>
       </c>
@@ -7492,7 +7495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>102</v>
       </c>
@@ -7527,7 +7530,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>103</v>
       </c>
@@ -7562,7 +7565,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -7597,7 +7600,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>105</v>
       </c>
@@ -7632,7 +7635,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>106</v>
       </c>
@@ -7667,7 +7670,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>108</v>
       </c>
@@ -7737,7 +7740,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>109</v>
       </c>
@@ -7772,7 +7775,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>110</v>
       </c>
@@ -7810,4 +7813,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{2f70ad68-4eca-4ffe-ad9d-60bfae449e23}" enabled="1" method="Standard" siteId="{b20a8f4d-0d6a-4f2e-83a2-181c968f8882}" removed="0"/>
+</clbl:labelList>
 </file>